--- a/artfynd/A 20744-2026 artfynd.xlsx
+++ b/artfynd/A 20744-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,27 +1273,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133478387</v>
+        <v>137489014</v>
       </c>
       <c r="B7" t="n">
-        <v>58658</v>
+        <v>43487</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>100943</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1301,25 +1301,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spännartorpet, Spännartorpet, Vstm</t>
+          <t>Spångabäcksområdet Yta 2:8 Spännartorpet, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507642</v>
+        <v>507730</v>
       </c>
       <c r="R7" t="n">
-        <v>6606882</v>
+        <v>6606814</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1343,22 +1348,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,48 +1364,67 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133478387</t>
+          <t>https://artportalen.se/Sighting/137489014</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54806505</v>
+        <v>133478387</v>
       </c>
       <c r="B8" t="n">
-        <v>43258</v>
+        <v>58658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>201129</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1418,33 +1432,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spännartorpet, Vstm</t>
+          <t>Spännartorpet, Spännartorpet, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507635</v>
+        <v>507642</v>
       </c>
       <c r="R8" t="n">
-        <v>6606800</v>
+        <v>6606882</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,12 +1474,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-08-10</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-08-10</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,16 +1504,131 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133478387</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>54806505</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spännartorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>507635</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6606800</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-08-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-08-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54806505</t>
         </is>
@@ -1512,6 +1643,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
